--- a/沪深300-中证500-中证1000-中证2000_夏普比率.xlsx
+++ b/沪深300-中证500-中证1000-中证2000_夏普比率.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12232" windowHeight="9555"/>
+    <workbookView windowWidth="20752" windowHeight="9555" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="沪深300" sheetId="1" r:id="rId1"/>
